--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>11</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>75:32</t>
+          <t>35:46</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>6</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>55:17</t>
+          <t>25:31</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>55:52</t>
+          <t>26:06</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>66:14</t>
+          <t>36:28</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>60:47</t>
+          <t>31:03</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>2</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>26:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>03:13</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>63:21</t>
+          <t>33:35</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -4488,10 +4488,10 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>45:36</t>
+          <t>25:51</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,22 +4604,22 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>13.7%</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>10.6%</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>13.6%</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>2</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>29:56</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -5272,10 +5272,10 @@
         <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.7%</t>
         </is>
       </c>
     </row>
@@ -5468,16 +5468,16 @@
         <v>45</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>11</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>70:03</t>
+          <t>30:17</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,22 +5584,22 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>03:32</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>-4</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>36:35</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>38:27</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,22 +6172,22 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>61:25</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,22 +6368,22 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>114</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>33</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>11</v>
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>6</v>
@@ -2315,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4488,10 +4488,10 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>2</v>
@@ -5272,16 +5272,16 @@
         <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>5</v>
@@ -5468,16 +5468,16 @@
         <v>45</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>11</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>-4</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>114</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X48" t="n">
         <v>33</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_399_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y41" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6264,14 +6264,14 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6796,14 +6796,14 @@
         <v>9</v>
       </c>
       <c r="X48" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
